--- a/ejemplos/Ejemplo_monopodico.xlsx
+++ b/ejemplos/Ejemplo_monopodico.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha predial" sheetId="6" state="visible" r:id="rIdFicha"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parámetros del ejemplo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="4" state="visible" r:id="rId4"/>
@@ -56275,4 +56276,116 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheetFicha.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Ficha predial</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Nombre del predio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Fundo Los Coigües (ejemplo ficticio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Rol de avalúo</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>1234-56</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Región</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Cautín</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Comuna</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Propietario</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Propietario de ejemplo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Antecedentes ficticios del ejemplo: no corresponden a un predio ni a personas reales.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>